--- a/empresas.xlsx
+++ b/empresas.xlsx
@@ -512,10 +512,8 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
+      <c r="J2" t="n">
+        <v>5970</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +560,8 @@
           <t>Rua Curitiba</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
+      <c r="J3" t="n">
+        <v>327</v>
       </c>
     </row>
     <row r="4">

--- a/empresas.xlsx
+++ b/empresas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,8 +469,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -484,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(31)99551-9546</t>
+          <t>(31) 99551-9546</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -504,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32.310-210</t>
+          <t>32310-210</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -512,13 +514,17 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5970</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -532,7 +538,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(31)3270-5443</t>
+          <t>(31) 3270-5443</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,7 +558,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30.170-120</t>
+          <t>30170-120</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,13 +566,17 @@
           <t>Rua Curitiba</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>327</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -580,7 +590,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(31)3392-8000</t>
+          <t>(31) 3392-8000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -600,7 +610,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>32.050-360</t>
+          <t>32050-360</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -608,13 +618,17 @@
           <t>Rua Apio Cardoso</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>505</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -628,7 +642,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(31)97244-5461</t>
+          <t>(31) 97244-5461</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -648,7 +662,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30.660-035</t>
+          <t>30660-035</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -656,13 +670,17 @@
           <t>Rua Maria Colares Pacheco</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>110</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -676,7 +694,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(31)98262-3214</t>
+          <t>(31) 98262-3214</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,7 +714,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>32.115-000</t>
+          <t>32115-000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -711,8 +729,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -726,7 +746,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(21)2110-7850</t>
+          <t>(21) 2110-7850</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,7 +766,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.775-005</t>
+          <t>22775-005</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -754,13 +774,17 @@
           <t>Avenida Ayrton Senna</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6000</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -774,7 +798,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(31)3965-1314</t>
+          <t>(31) 3965-1314</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -794,7 +818,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.310-210</t>
+          <t>32310-210</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -802,13 +826,17 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5796</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -842,7 +870,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.310-160</t>
+          <t>32310-160</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -850,13 +878,17 @@
           <t>Rua General Eurico Gaspar Dutra</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>37</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -870,7 +902,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(31) 3283 4949</t>
+          <t>(31) 3283-4949</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -890,7 +922,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.120-040</t>
+          <t>30120-040</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -905,8 +937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -940,7 +974,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>39.538-000</t>
+          <t>39538-000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -948,13 +982,17 @@
           <t>Rua Gasparino Gomes</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>82</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -968,7 +1006,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(31)3515-7400</t>
+          <t>(31) 3515-7400</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -988,7 +1026,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.150-050</t>
+          <t>30150-050</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,8 +1041,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1018,7 +1058,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(31) 98796 4293</t>
+          <t>(31) 98796-4293</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1038,7 +1078,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31.560-300</t>
+          <t>31560-300</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1046,13 +1086,17 @@
           <t>Avenida Guarapari</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>826</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1066,7 +1110,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(31)3287-0007</t>
+          <t>(31) 3287-0007</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1086,7 +1130,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.130-131</t>
+          <t>30130-131</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1101,8 +1145,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1116,7 +1162,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(31)2555-7451</t>
+          <t>(31) 2555-7451</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1136,7 +1182,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31.010-150</t>
+          <t>31010-150</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,13 +1190,17 @@
           <t>Rua Nefelina</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>14</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1164,7 +1214,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(31)3447-9803</t>
+          <t>(31) 3447-9803</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1184,7 +1234,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30.130-162</t>
+          <t>30130-162</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1199,8 +1249,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1214,7 +1266,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(31)3527-7075</t>
+          <t>(31) 3527-7075</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1234,7 +1286,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30.140-006</t>
+          <t>30140-006</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1242,13 +1294,17 @@
           <t>Avenida Brasil</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>1912</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1262,7 +1318,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(31) 98324 8736</t>
+          <t>(31) 98324-8736</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1282,7 +1338,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30.130-171</t>
+          <t>30130-171</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1297,8 +1353,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1312,7 +1370,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(31)3451-1200</t>
+          <t>(31) 3451-1200</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1332,7 +1390,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>31.515-100</t>
+          <t>31515-100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1340,13 +1398,17 @@
           <t>Rua Santo Antonio</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>424</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1360,7 +1422,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(11)3251-4597</t>
+          <t>(11) 3251-4597</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1380,7 +1442,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01.326-010</t>
+          <t>01326-010</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1388,13 +1450,17 @@
           <t>Rua Rui Barbosa</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>192</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1408,7 +1474,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(11)3286-9090</t>
+          <t>(11) 3286-9090</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1428,7 +1494,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01.330-000</t>
+          <t>01330-000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1436,13 +1502,17 @@
           <t>Rua Rocha</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>343</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1456,7 +1526,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(11)99707-6032</t>
+          <t>(11) 99707-6032</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1476,7 +1546,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01.332-901</t>
+          <t>01332-901</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1491,8 +1561,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1506,7 +1578,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(11)3253-5676</t>
+          <t>(11) 3253-5676</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1526,7 +1598,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01.311-200</t>
+          <t>01311-200</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1541,8 +1613,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1556,7 +1630,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(21)99683-3398</t>
+          <t>(21) 99683-3398</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1576,7 +1650,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22.031-071</t>
+          <t>22031-071</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1591,8 +1665,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1606,7 +1682,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(21)2549-8000</t>
+          <t>(21) 2549-8000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1626,7 +1702,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22.031-010</t>
+          <t>22031-010</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1641,8 +1717,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1656,7 +1734,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(21)2235-2264</t>
+          <t>(21) 2235-2264</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1676,7 +1754,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22.031-071</t>
+          <t>22031-071</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1691,8 +1769,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(21)98188-5751</t>
+          <t>(21) 98188-5751</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1726,7 +1806,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25.010-145</t>
+          <t>25010-145</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1734,13 +1814,17 @@
           <t>Avenida Nilo Pecanha</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>321</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1754,7 +1838,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(21)2688-3035</t>
+          <t>(21) 2688-3035</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1774,7 +1858,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23.815-460</t>
+          <t>23815-460</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1782,13 +1866,17 @@
           <t>Rua Moises Abraão</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>42</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1822,7 +1910,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25.010-144</t>
+          <t>25010-144</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1837,8 +1925,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1852,7 +1942,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(38)3821-2220</t>
+          <t>(38) 3821-2220</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1872,7 +1962,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>39.447-339</t>
+          <t>39447-339</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1880,13 +1970,17 @@
           <t>Avenida Manoel Athaide</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>2548</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2548</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1900,7 +1994,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(34)3845-1686</t>
+          <t>(34) 3845-1686</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1920,7 +2014,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>38.510-000</t>
+          <t>38510-000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1928,13 +2022,17 @@
           <t>Avenida Sete de Setembro</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>392</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1948,7 +2046,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(31)3391-3770</t>
+          <t>(31) 3391-3770</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1968,7 +2066,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>32.315-120</t>
+          <t>32315-120</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1976,13 +2074,17 @@
           <t>Rua Ingás</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>581</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1996,7 +2098,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(31)3198-7000</t>
+          <t>(31) 3198-7000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2016,7 +2118,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>32.310-210</t>
+          <t>32310-210</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2024,13 +2126,17 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>4257</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2044,7 +2150,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(31)3395-2003</t>
+          <t>(31) 3395-2003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2064,7 +2170,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>32.315-040</t>
+          <t>32315-040</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2072,13 +2178,17 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>6190</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2092,7 +2202,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(31)2568-5901</t>
+          <t>(31) 2568-5901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2112,7 +2222,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>32.310-210</t>
+          <t>32310-210</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2120,13 +2230,17 @@
           <t>Avenida Jose Faria da Rocha</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>4662</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4662</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2140,7 +2254,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(31)2524-5654</t>
+          <t>(31) 2524-5654</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2160,7 +2274,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>32.340-030</t>
+          <t>32340-030</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2168,13 +2282,17 @@
           <t>Rua Belgica</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>702</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2188,7 +2306,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(31)2557-8890</t>
+          <t>(31) 2557-8890</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2208,7 +2326,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>32.340-030</t>
+          <t>32340-030</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2216,13 +2334,17 @@
           <t>Rua Belgica</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>682</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2236,7 +2358,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(31)99137-7213</t>
+          <t>(31) 99137-7213</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2256,21 +2378,25 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>32.340-130</t>
+          <t>32340-130</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Rua Inglaterra</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>681</v>
+          <t>Rua Inglaterra</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2284,7 +2410,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(31)3565-7566</t>
+          <t>(31) 3565-7566</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2304,7 +2430,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>31.515-320</t>
+          <t>31515-320</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2312,13 +2438,17 @@
           <t>Rua Cyrene Crivellari Bellonia</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>39</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2332,7 +2462,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(31)3271-4083</t>
+          <t>(31) 3271-4083</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2352,7 +2482,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>30.170-120</t>
+          <t>30170-120</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2360,13 +2490,17 @@
           <t>Rua Curitiba</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>194</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2380,7 +2514,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(31)99510-1851</t>
+          <t>(31) 99510-1851</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2400,7 +2534,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>13.403-00</t>
+          <t>1340300</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2408,13 +2542,17 @@
           <t>Avenida Madre Maria Teodora'</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>201</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2428,7 +2566,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(31)3773-5768</t>
+          <t>(31) 3773-5768</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2448,7 +2586,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>35.700-071</t>
+          <t>35700-071</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2456,13 +2594,17 @@
           <t>Rua Major Castanheira</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>262</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2496,7 +2638,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>07.700-625</t>
+          <t>07700-625</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2504,13 +2646,17 @@
           <t>Avenida dos Estudantes</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>45</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2524,7 +2670,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(31)99971-6889</t>
+          <t>(31) 99971-6889</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2544,7 +2690,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>35.700-049</t>
+          <t>35700-049</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2552,13 +2698,17 @@
           <t>Rua Paulo Frontin</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>1219</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2572,7 +2722,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(31)99941-8297</t>
+          <t>(31) 99941-8297</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2592,7 +2742,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>35.700-049</t>
+          <t>35700-049</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2600,13 +2750,17 @@
           <t>Rua Paulo Frontin</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>1229</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2620,7 +2774,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(31)3771-5931</t>
+          <t>(31) 3771-5931</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2640,7 +2794,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>35.700-034</t>
+          <t>35700-034</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2648,13 +2802,17 @@
           <t>Rua Conego Raimundo</t>
         </is>
       </c>
-      <c r="J46" t="n">
-        <v>94</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2668,7 +2826,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(38)98831-5889</t>
+          <t>(38) 98831-5889</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2688,7 +2846,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>38.779-000</t>
+          <t>38779-000</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2696,13 +2854,17 @@
           <t>Rua Izau Luiz Ferreira</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>537</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2716,7 +2878,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(31)3776-7675</t>
+          <t>(31) 3776-7675</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2736,7 +2898,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>35.700-041</t>
+          <t>35700-041</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2744,13 +2906,17 @@
           <t>Rua Monsenhor Messias</t>
         </is>
       </c>
-      <c r="J48" t="n">
-        <v>307</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2764,7 +2930,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(31)3771-0114</t>
+          <t>(31) 3771-0114</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2779,12 +2945,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Centro</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>35.700-041</t>
+          <t>35700-041</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2792,13 +2958,17 @@
           <t>Rua Monsenhor Messias</t>
         </is>
       </c>
-      <c r="J49" t="n">
-        <v>273</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2812,7 +2982,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(31)3773-1931</t>
+          <t>(31) 3773-1931</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2832,7 +3002,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>35.700-041</t>
+          <t>35700-041</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2840,13 +3010,17 @@
           <t>Rua Monsenhor Messias</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>379</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2860,7 +3034,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(31)99503-5414</t>
+          <t>(31) 99503-5414</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2880,7 +3054,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>33.880-400</t>
+          <t>33880-400</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2888,13 +3062,17 @@
           <t>Rua Ana Maria de Jesus</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>85</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2908,7 +3086,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(75)99810-0023</t>
+          <t>(75) 99810-0023</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2928,7 +3106,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>46.960-000</t>
+          <t>46960-000</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2936,13 +3114,17 @@
           <t>Praca Horacio de Matos</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>14</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2956,7 +3138,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(31)3384-1198</t>
+          <t>(31) 3384-1198</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2976,7 +3158,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>30.640-520</t>
+          <t>30640-520</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2984,13 +3166,17 @@
           <t>Rua Benjamim Dias</t>
         </is>
       </c>
-      <c r="J53" t="n">
-        <v>379</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3024,7 +3210,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>30.160-909</t>
+          <t>30160-909</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3032,13 +3218,17 @@
           <t>Rua Rio de Janeiro</t>
         </is>
       </c>
-      <c r="J54" t="n">
-        <v>462</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3052,7 +3242,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(31)3166-6026</t>
+          <t>(31) 3166-6026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3072,7 +3262,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>30.775-450</t>
+          <t>30775-450</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3080,13 +3270,17 @@
           <t>Rua Lambda</t>
         </is>
       </c>
-      <c r="J55" t="n">
-        <v>150</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3100,7 +3294,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(31)2510-6130</t>
+          <t>(31) 2510-6130</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3120,7 +3314,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>31.275-030</t>
+          <t>31275-030</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3128,13 +3322,17 @@
           <t>Rua Roquete Mendonça</t>
         </is>
       </c>
-      <c r="J56" t="n">
-        <v>561</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3148,7 +3346,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(31)3426-1948</t>
+          <t>(31) 3426-1948</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3168,7 +3366,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>31.910-900</t>
+          <t>31910-900</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3176,13 +3374,17 @@
           <t>Avenida Cristiano Machado</t>
         </is>
       </c>
-      <c r="J57" t="n">
-        <v>4000</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3196,7 +3398,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(33)98844-1032</t>
+          <t>(33) 98844-1032</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3216,7 +3418,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>39.920-000</t>
+          <t>39920-000</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3224,13 +3426,17 @@
           <t>Rua Jose Trancoso de Meireles</t>
         </is>
       </c>
-      <c r="J58" t="n">
-        <v>33</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3244,7 +3450,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(31)3229-6040</t>
+          <t>(31) 3229-6040</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3264,7 +3470,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>30.140-120</t>
+          <t>30140-120</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3272,8 +3478,62 @@
           <t>Rua dos Inconfidentes</t>
         </is>
       </c>
-      <c r="J59" t="n">
-        <v>44</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Beleaf Industria e Comercio de Alimentos S.a.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>24.296.895/0001-11</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>(11) 3181-8927</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chacara Santo Antonio</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0471400</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Rua Antonio das Chagas</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
       </c>
     </row>
   </sheetData>
